--- a/data/nzd0274/nzd0274.xlsx
+++ b/data/nzd0274/nzd0274.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G363"/>
+  <dimension ref="A1:G365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10233,6 +10233,60 @@
         <v>330.68</v>
       </c>
       <c r="G363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>315.47</v>
+      </c>
+      <c r="C364" t="n">
+        <v>281.94</v>
+      </c>
+      <c r="D364" t="n">
+        <v>312.53</v>
+      </c>
+      <c r="E364" t="n">
+        <v>327.41</v>
+      </c>
+      <c r="F364" t="n">
+        <v>332.28</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>317.13</v>
+      </c>
+      <c r="C365" t="n">
+        <v>278.66</v>
+      </c>
+      <c r="D365" t="n">
+        <v>312.64</v>
+      </c>
+      <c r="E365" t="n">
+        <v>327.03</v>
+      </c>
+      <c r="F365" t="n">
+        <v>331.93</v>
+      </c>
+      <c r="G365" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10249,7 +10303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B395"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14202,6 +14256,26 @@
       </c>
       <c r="B395" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
@@ -14370,28 +14444,28 @@
         <v>0.0885</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1237775897586728</v>
+        <v>-0.1199235469928316</v>
       </c>
       <c r="J2" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K2" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02584348413265602</v>
+        <v>0.02450124879400672</v>
       </c>
       <c r="M2" t="n">
-        <v>4.491143714905702</v>
+        <v>4.482377601930716</v>
       </c>
       <c r="N2" t="n">
-        <v>32.65393498058566</v>
+        <v>32.55454469978167</v>
       </c>
       <c r="O2" t="n">
-        <v>5.714362167432657</v>
+        <v>5.705659006616297</v>
       </c>
       <c r="P2" t="n">
-        <v>315.8421815535619</v>
+        <v>315.8011277296917</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14448,28 +14522,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3632781064567757</v>
+        <v>-0.3708921575234938</v>
       </c>
       <c r="J3" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K3" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02060511594215975</v>
+        <v>0.02167338002373598</v>
       </c>
       <c r="M3" t="n">
-        <v>14.92991189816939</v>
+        <v>14.89412713063733</v>
       </c>
       <c r="N3" t="n">
-        <v>355.513475931611</v>
+        <v>353.8671535348207</v>
       </c>
       <c r="O3" t="n">
-        <v>18.85506499409671</v>
+        <v>18.8113570359722</v>
       </c>
       <c r="P3" t="n">
-        <v>297.3838167902361</v>
+        <v>297.4647969497208</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14526,28 +14600,28 @@
         <v>0.193</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2260052929717396</v>
+        <v>-0.22348654671977</v>
       </c>
       <c r="J4" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K4" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07777477537307476</v>
+        <v>0.07689307389368483</v>
       </c>
       <c r="M4" t="n">
-        <v>4.255089772270236</v>
+        <v>4.244627162408873</v>
       </c>
       <c r="N4" t="n">
-        <v>34.24595296736702</v>
+        <v>34.09037311375123</v>
       </c>
       <c r="O4" t="n">
-        <v>5.852004183813185</v>
+        <v>5.838696182689354</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1476542336577</v>
+        <v>316.1208269480916</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14604,28 +14678,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1705166023333529</v>
+        <v>-0.1624001080348224</v>
       </c>
       <c r="J5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09966092327593812</v>
+        <v>0.09028004669650713</v>
       </c>
       <c r="M5" t="n">
-        <v>2.805544755981542</v>
+        <v>2.830411969302727</v>
       </c>
       <c r="N5" t="n">
-        <v>14.88007060996527</v>
+        <v>15.13758027685149</v>
       </c>
       <c r="O5" t="n">
-        <v>3.857469456776718</v>
+        <v>3.890704341999208</v>
       </c>
       <c r="P5" t="n">
-        <v>323.8432383150526</v>
+        <v>323.7568241435195</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14682,28 +14756,28 @@
         <v>0.131</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3505437564706959</v>
+        <v>-0.3436643708645639</v>
       </c>
       <c r="J6" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K6" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3162642335725389</v>
+        <v>0.3066633957619102</v>
       </c>
       <c r="M6" t="n">
-        <v>2.941984262243418</v>
+        <v>2.958513485632899</v>
       </c>
       <c r="N6" t="n">
-        <v>15.02091867877162</v>
+        <v>15.18152521500916</v>
       </c>
       <c r="O6" t="n">
-        <v>3.875682995134099</v>
+        <v>3.896347676351427</v>
       </c>
       <c r="P6" t="n">
-        <v>334.7341120847674</v>
+        <v>334.6608412742766</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14741,7 +14815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G363"/>
+  <dimension ref="A1:G365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28167,6 +28241,80 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-38.79991091194617,174.58980493498996</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-38.79933009996006,174.59044378633467</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-38.79858270628595,174.5903757616744</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-38.797876118954115,174.59048093136565</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-38.79719553021228,174.59069645376653</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-38.79990659942601,174.58978663457466</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-38.799338620910106,174.59047994596054</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-38.79858242052026,174.59037454901753</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-38.79787710614485,174.59048512050236</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-38.79719643946346,174.59070031214634</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0274/nzd0274.xlsx
+++ b/data/nzd0274/nzd0274.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G365"/>
+  <dimension ref="A1:G366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10289,6 +10289,33 @@
       <c r="G365" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>317.06</v>
+      </c>
+      <c r="C366" t="n">
+        <v>278.66</v>
+      </c>
+      <c r="D366" t="n">
+        <v>312.64</v>
+      </c>
+      <c r="E366" t="n">
+        <v>327.03</v>
+      </c>
+      <c r="F366" t="n">
+        <v>332.46</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14276,6 +14303,16 @@
       </c>
       <c r="B397" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -14444,28 +14481,28 @@
         <v>0.0885</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1199235469928316</v>
+        <v>-0.117651486161069</v>
       </c>
       <c r="J2" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K2" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02450124879400672</v>
+        <v>0.02369092900260261</v>
       </c>
       <c r="M2" t="n">
-        <v>4.482377601930716</v>
+        <v>4.479685826619622</v>
       </c>
       <c r="N2" t="n">
-        <v>32.55454469978167</v>
+        <v>32.5192016311041</v>
       </c>
       <c r="O2" t="n">
-        <v>5.705659006616297</v>
+        <v>5.702560971274582</v>
       </c>
       <c r="P2" t="n">
-        <v>315.8011277296917</v>
+        <v>315.7768906528368</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14522,28 +14559,28 @@
         <v>0.0526</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3708921575234938</v>
+        <v>-0.3754502156328313</v>
       </c>
       <c r="J3" t="n">
+        <v>365</v>
+      </c>
+      <c r="K3" t="n">
         <v>364</v>
       </c>
-      <c r="K3" t="n">
-        <v>363</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02167338002373598</v>
+        <v>0.02230289588809986</v>
       </c>
       <c r="M3" t="n">
-        <v>14.89412713063733</v>
+        <v>14.88087774754713</v>
       </c>
       <c r="N3" t="n">
-        <v>353.8671535348207</v>
+        <v>353.1118119259487</v>
       </c>
       <c r="O3" t="n">
-        <v>18.8113570359722</v>
+        <v>18.79126956663516</v>
       </c>
       <c r="P3" t="n">
-        <v>297.4647969497208</v>
+        <v>297.5133445212709</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14600,28 +14637,28 @@
         <v>0.193</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.22348654671977</v>
+        <v>-0.2222230703626481</v>
       </c>
       <c r="J4" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K4" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07689307389368483</v>
+        <v>0.07644155916333906</v>
       </c>
       <c r="M4" t="n">
-        <v>4.244627162408873</v>
+        <v>4.239438841785359</v>
       </c>
       <c r="N4" t="n">
-        <v>34.09037311375123</v>
+        <v>34.01362657004789</v>
       </c>
       <c r="O4" t="n">
-        <v>5.838696182689354</v>
+        <v>5.832120246535379</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1208269480916</v>
+        <v>316.107348887494</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14678,28 +14715,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1624001080348224</v>
+        <v>-0.1585233914885807</v>
       </c>
       <c r="J5" t="n">
+        <v>365</v>
+      </c>
+      <c r="K5" t="n">
         <v>364</v>
       </c>
-      <c r="K5" t="n">
-        <v>363</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.09028004669650713</v>
+        <v>0.08600160850812633</v>
       </c>
       <c r="M5" t="n">
-        <v>2.830411969302727</v>
+        <v>2.842776206068986</v>
       </c>
       <c r="N5" t="n">
-        <v>15.13758027685149</v>
+        <v>15.25325842611996</v>
       </c>
       <c r="O5" t="n">
-        <v>3.890704341999208</v>
+        <v>3.90554201438417</v>
       </c>
       <c r="P5" t="n">
-        <v>323.7568241435195</v>
+        <v>323.7154849439854</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14756,28 +14793,28 @@
         <v>0.131</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3436643708645639</v>
+        <v>-0.340113550586862</v>
       </c>
       <c r="J6" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K6" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3066633957619102</v>
+        <v>0.3015904537217191</v>
       </c>
       <c r="M6" t="n">
-        <v>2.958513485632899</v>
+        <v>2.967524917253561</v>
       </c>
       <c r="N6" t="n">
-        <v>15.18152521500916</v>
+        <v>15.27144924953515</v>
       </c>
       <c r="O6" t="n">
-        <v>3.896347676351427</v>
+        <v>3.907870167947644</v>
       </c>
       <c r="P6" t="n">
-        <v>334.6608412742766</v>
+        <v>334.6229631053623</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14815,7 +14852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G365"/>
+  <dimension ref="A1:G366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28315,6 +28352,43 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-38.799906781279326,174.5897874062789</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-38.799338620910106,174.59047994596054</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-38.79858242052026,174.59037454901753</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-38.79787710614485,174.59048512050236</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-38.79719506259733,174.59069446945693</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
